--- a/Week 2 assignments.xlsx
+++ b/Week 2 assignments.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GenAI\Assignments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2C1EB0-D6FF-4935-990B-0E0A1C578A45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4FE5FB9-C301-4AE8-80F6-90AE257BD21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F242FC1A-52A3-4BC0-8027-9E04E500FA69}"/>
   </bookViews>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="573">
   <si>
     <t>Please complete the following API requests on postman collection</t>
   </si>
@@ -2238,7 +2236,240 @@
     <t>Drove continuous improvement culture within QA function.</t>
   </si>
   <si>
-    <t>Yet to start</t>
+    <t>API response</t>
+  </si>
+  <si>
+    <t>200 OK</t>
+  </si>
+  <si>
+    <t>{
+    "id": "chatcmpl-7fa8d15a-26ff-4ba6-8200-76a593819fd6",
+    "object": "chat.completion",
+    "created": 1771855952,
+    "model": "meta-llama/llama-4-scout-17b-16e-instruct",
+    "choices": [
+        {
+            "index": 0,
+            "message": {
+                "role": "assistant",
+                "content": "- WCAG_Level: A\n- WCAG_Criterion: 1.1.1 Non-text Content \n- Observation: The image with url \"http://leaftaps.com/opentaps_images/opentaps_logo.png\" does not have a text alternative.\n- Compliance_Status: Non-Compliant\n- Evidence: image url: http://leaftaps.com/opentaps_images/opentaps_logo.png\n\n- WCAG_Level: A\n- WCAG_Criterion: 1.3.1 Info and Relationships \n- Observation: The StaticText \"Username\" and \"Password\" are not associated with their corresponding textboxes.\n- Compliance_Status: Non-Compliant\n- Evidence: paragraph &gt; LabelText &gt; StaticText \"Username\" and textbox \"Username\", paragraph &gt; LabelText &gt; StaticText \"Password\" and textbox \"Password\"\n\n- WCAG_Level: A\n- WCAG_Criterion: 1.3.2 Meaningful Sequence \n- Observation: The order of the elements in the Accessibility DOM seems logical.\n- Compliance_Status: Compliant\n- Evidence: The provided Accessibility DOM\n\n- WCAG_Level: A\n- WCAG_Criterion: 2.1.1 Keyboard Navigation \n- Observation: The textbox \"Username\", textbox \"Password\" and button \"Login\" are focusable.\n- Compliance_Status: Compliant\n- Evidence: textbox \"Username\" &gt; focusable: true, textbox \"Password\" &gt; focusable: true, button \"Login\" &gt; focusable: true\n\n- WCAG_Level: A\n- WCAG_Criterion: 2.1.3 Keyboard-Operable \n- Observation: There is no information about the operability of the controls using a keyboard.\n- Compliance_Status: Potential Risk\n- Evidence: The provided Accessibility DOM\n\n- WCAG_Level: A\n- WCAG_Criterion: 3.1.1 Language of Page \n- Observation: There is no clear indication of the language of the page.\n- Compliance_Status: Potential Risk\n- Evidence: The provided Accessibility DOM\n\n- WCAG_Level: AA\n- WCAG_Criterion: 1.4.7 Visual Presentation \n- Observation: There is no information about the visual presentation of the blocks of text.\n- Compliance_Status: Potential Risk\n- Evidence: The provided Accessibility DOM\n\n- WCAG_Level: AA\n- WCAG_Criterion: 2.4.6 Headings and Labels \n- Observation: The labels for the textboxes are provided but not explicitly associated.\n- Compliance_Status: Non-Compliant\n- Evidence: paragraph &gt; LabelText &gt; StaticText \"Username\" and textbox \"Username\", paragraph &gt; LabelText &gt; StaticText \"Password\" and textbox \"Password\"\n\n- WCAG_Level: AAA\n- WCAG_Criterion: 1.4.8 Visual Presentation \n- Observation: There is no information about the visual presentation of the blocks of text.\n- Compliance_Status: Potential Risk\n- Evidence: The provided Accessibility DOM\n\n- WCAG_Level: AAA\n- WCAG_Criterion: 2.4.9 Link Purpose \n- Observation: There are no links in the provided Accessibility DOM.\n- Compliance_Status: Compliant\n- Evidence: The provided Accessibility DOM \n\n- WCAG_Level: AAA\n- WCAG_Criterion: 3.1.3 Error Prevention \n- Observation: There is no information about the prevention of errors.\n- Compliance_Status: Potential Risk\n- Evidence: The provided Accessibility DOM"
+            },
+            "logprobs": null,
+            "finish_reason": "stop"
+        }
+    ],
+    "usage": {
+        "queue_time": 0.044391259,
+        "prompt_tokens": 524,
+        "prompt_time": 0.016238341,
+        "completion_tokens": 705,
+        "completion_time": 1.655305889,
+        "total_tokens": 1229,
+        "total_time": 1.6715442299999999
+    },
+    "usage_breakdown": null,
+    "system_fingerprint": "fp_37da608fc1",
+    "x_groq": {
+        "id": "req_01kj5dgcq7fgnb5zkjtch82phb",
+        "seed": 570979609
+    },
+    "service_tier": "on_demand"
+}</t>
+  </si>
+  <si>
+    <t>{
+    "id": "chatcmpl-01341ba0-5b41-4567-b112-2d89ae6193b1",
+    "object": "chat.completion",
+    "created": 1771856194,
+    "model": "meta-llama/llama-4-scout-17b-16e-instruct",
+    "choices": [
+        {
+            "index": 0,
+            "message": {
+                "role": "assistant",
+                "content": "Here are the test cases derived from the provided User Story and Acceptance Criteria:\n\n**TC_ID:1**\n- **Title:** Record Doctor Activity Successfully\n- **Preconditions:** The system is operational, and the user is logged in with necessary permissions.\n- **Test Steps:**\n  1. Navigate to the doctor activity recording section.\n  2. Select a doctor from the available list.\n  3. Choose the activity type (e.g., patient consultation, surgery).\n  4. Enter detailed notes about the activity.\n  5. Save the activity record.\n- **Test Data:** Valid doctor name, activity type, and notes.\n- **Expected Result:** The system saves the doctor activity record successfully, and it is visible in the activity log. **(Positive)**\n\n**TC_ID:2**\n- **Title:** Record Doctor Activity with Empty Notes\n- **Preconditions:** The system is operational, and the user is logged in with necessary permissions.\n- **Test Steps:**\n  1. Navigate to the doctor activity recording section.\n  2. Select a doctor from the available list.\n  3. Choose the activity type (e.g., patient consultation, surgery).\n  4. Save the activity record without entering notes.\n- **Test Data:** Valid doctor name, activity type, but empty notes.\n- **Expected Result:** The system prevents saving the record and prompts the user to enter notes. **(Negative)**\n\n**TC_ID:3**\n- **Title:** Record Doctor Activity with Invalid Doctor Selection\n- **Preconditions:** The system is operational, and the user is logged in with necessary permissions.\n- **Test Steps:**\n  1. Navigate to the doctor activity recording section.\n  2. Attempt to save the activity record without selecting a doctor.\n  3. Verify the system's response.\n- **Test Data:** No doctor selected, valid activity type, and notes.\n- **Expected Result:** The system prevents saving the record and prompts the user to select a doctor. **(Negative)**\n\n**TC_ID:4**\n- **Title:** View Recorded Doctor Activities\n- **Preconditions:** There are existing doctor activity records, and the user is logged in with necessary permissions.\n- **Test Steps:**\n  1. Navigate to the doctor activity log section.\n  2. Search or filter activities by doctor, date, or activity type.\n  3. Verify the displayed activity records match the search/filter criteria.\n- **Test Data:** Existing doctor activity records, valid search/filter criteria.\n- **Expected Result:** The system displays the correct doctor activity records based on the search/filter criteria. **(Positive)**\n\n**TC_ID:5**\n- **Title:** Edit Recorded Doctor Activity\n- **Preconditions:** There are existing doctor activity records, and the user is logged in with necessary permissions.\n- **Test Steps:**\n  1. Navigate to the doctor activity log section.\n  2. Locate an existing activity record.\n  3. Edit the activity details (e.g., activity type, notes).\n  4. Save the changes.\n- **Test Data:** Existing doctor activity record, updated activity details.\n- **Expected Result:** The system updates the doctor activity record successfully, and the changes are reflected in the activity log. **(Positive)**\n\n**TC_ID"
+            },
+            "logprobs": null,
+            "finish_reason": "stop"
+        }
+    ],
+    "usage": {
+        "queue_time": 0.044394446,
+        "prompt_tokens": 302,
+        "prompt_time": 0.009094264,
+        "completion_tokens": 1255,
+        "completion_time": 3.168714832,
+        "total_tokens": 1557,
+        "total_time": 3.177809096
+    },
+    "usage_breakdown": null,
+    "system_fingerprint": "fp_79da0e0073",
+    "x_groq": {
+        "id": "req_01kj5dqr6gebhbsp469mgke8jw",
+        "seed": 1918799300
+    },
+    "service_tier": "on_demand"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "id": "chatcmpl-01341ba0-5b41-4567-b112-2d89ae6193b1",
+  "object": "chat.completion",
+  "created": 1771856194,
+  "model": "meta-llama/llama-4-scout-17b-16e-instruct",
+  "choices": [
+    {
+      "index": 0,
+      "message": {
+        "role": "assistant",
+        "content": "Here are the test cases derived from the provided User Story and Acceptance Criteria:\n\n**TC_ID:1**\n- **Title:** Record Doctor Activity Successfully\n- **Preconditions:** The system is operational, and the user is logged in with necessary permissions.\n- **Test Steps:**\n  1. Navigate to the doctor activity recording section.\n  2. Select a doctor from the available list.\n  3. Choose the activity type (e.g., patient consultation, surgery).\n  4. Enter detailed notes about the activity.\n  5. Save the activity record.\n- **Test Data:** Valid doctor name, activity type, and notes.\n- **Expected Result:** The system saves the doctor activity record successfully, and it is visible in the activity log. **(Positive)**\n\n**TC_ID:2**\n- **Title:** Record Doctor Activity with Empty Notes\n- **Preconditions:** The system is operational, and the user is logged in with necessary permissions.\n- **Test Steps:**\n  1. Navigate to the doctor activity recording section.\n  2. Select a doctor from the available list.\n  3. Choose the activity type (e.g., patient consultation, surgery).\n  4. Save the activity record without entering notes.\n- **Test Data:** Valid doctor name, activity type, but empty notes.\n- **Expected Result:** The system prevents saving the record and prompts the user to enter notes. **(Negative)**\n\n**TC_ID:3**\n- **Title:** Record Doctor Activity with Invalid Doctor Selection\n- **Preconditions:** The system is operational, and the user is logged in with necessary permissions.\n- **Test Steps:**\n  1. Navigate to the doctor activity recording section.\n  2. Attempt to save the activity record without selecting a doctor.\n  3. Verify the system's response.\n- **Test Data:** No doctor selected, valid activity type, and notes.\n- **Expected Result:** The system prevents saving the record and prompts the user to select a doctor. **(Negative)**\n\n**TC_ID:4**\n- **Title:** View Recorded Doctor Activities\n- **Preconditions:** There are existing doctor activity records, and the user is logged in with necessary permissions.\n- **Test Steps:**\n  1. Navigate to the doctor activity log section.\n  2. Search or filter activities by doctor, date, or activity type.\n  3. Verify the displayed activity records match the search/filter criteria.\n- **Test Data:** Existing doctor activity records, valid search/filter criteria.\n- **Expected Result:** The system displays the correct doctor activity records based on the search/filter criteria. **(Positive)**\n\n**TC_ID:5**\n- **Title:** Edit Recorded Doctor Activity\n- **Preconditions:** There are existing doctor activity records, and the user is logged in with necessary permissions.\n- **Test Steps:**\n  1. Navigate to the doctor activity log section.\n  2. Locate an existing activity record.\n  3. Edit the activity details (e.g., activity type, notes).\n  4. Save the changes.\n- **Test Data:** Existing doctor activity record, updated activity details.\n- **Expected Result:** The system updates the doctor activity record successfully, and the changes are reflected in the activity log. **(Positive)**\n\n**TC_ID"
+      },
+      "logprobs": null,
+      "finish_reason": "stop"
+    }
+  ],
+  "usage": {
+    "queue_time": 0.044394446,
+    "prompt_tokens": 302,
+    "prompt_time": 0.009094264,
+    "completion_tokens": 1255,
+    "completion_time": 3.168714832,
+    "total_tokens": 1557,
+    "total_time": 3.177809096
+  },
+  "usage_breakdown": null,
+  "system_fingerprint": "fp_79da0e0073",
+  "x_groq": {
+    "id": "req_01kj5dqr6gebhbsp469mgke8jw",
+    "seed": 1918799300
+  },
+  "service_tier": "on_demand"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "id": "chatcmpl-f43fcff1-73d1-4373-a058-52e640d66117",
+  "object": "chat.completion",
+  "created": 1771858685,
+  "model": "meta-llama/llama-4-scout-17b-16e-instruct",
+  "choices": [
+    {
+      "index": 0,
+      "message": {
+        "role": "assistant",
+        "content": "1. Valid Patient Registration with Complete Details.\n2. Patient Registration with Missing Required Fields.\n3. Registration with Invalid Patient Identification Number.\n4. Successful Registration with Insurance Details.\n5. Registration with Incorrect Admission Type.\n6. Patient Registration with Duplicate Patient ID.\n7. Inpatient Registration with Incomplete Address.\n8. Registration with Valid and Existing Insurance Provider.\n9. Patient Registration with Multiple Admission Types.\n10. Confirmation of Patient Registration with Unique Identifier."
+      },
+      "logprobs": null,
+      "finish_reason": "stop"
+    }
+  ],
+  "usage": {
+    "queue_time": 0.058753267,
+    "prompt_tokens": 130,
+    "prompt_time": 0.003758073,
+    "completion_tokens": 91,
+    "completion_time": 0.21061218,
+    "total_tokens": 221,
+    "total_time": 0.214370253
+  },
+  "usage_breakdown": null,
+  "system_fingerprint": "fp_37da608fc1",
+  "x_groq": {
+    "id": "req_01kj5g3vmjfmtv54fkvvq7fa1e",
+    "seed": 1243657094
+  },
+  "service_tier": "on_demand"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "id": "chatcmpl-283e2061-57d0-4fde-85fa-f1960a2c21d4",
+  "object": "chat.completion",
+  "created": 1771859040,
+  "model": "meta-llama/llama-4-scout-17b-16e-instruct",
+  "choices": [
+    {
+      "index": 0,
+      "message": {
+        "role": "assistant",
+        "content": "1. Valid Patient Registration with Complete Details.\n2. Patient Registration with Missing Required Fields.\n3. Registration with Invalid Patient Identification Number.\n4. Successful Registration with Insurance Details.\n5. Registration with Incorrect Admission Type.\n6. Patient Registration with Duplicate Patient ID.\n7. Inpatient Registration with Multiple Insurance Providers.\n8. Validation of Patient Address and Contact Information.\n9. Registration Confirmation with Patient and Admission Details.\n10. Emergency Admission Registration with Minimal Information."
+      },
+      "logprobs": null,
+      "finish_reason": "stop"
+    }
+  ],
+  "usage": {
+    "queue_time": 0.044249095,
+    "prompt_tokens": 130,
+    "prompt_time": 0.003223001,
+    "completion_tokens": 92,
+    "completion_time": 0.219328043,
+    "total_tokens": 222,
+    "total_time": 0.222551044
+  },
+  "usage_breakdown": null,
+  "system_fingerprint": "fp_37da608fc1",
+  "x_groq": {
+    "id": "req_01kj5genj0e3jrwrxjz6snhrsx",
+    "seed": 715187179
+  },
+  "service_tier": "on_demand"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "id": "chatcmpl-46aba7b3-d6d3-4a70-8c45-7743bb3247f5",
+  "object": "chat.completion",
+  "created": 1771859450,
+  "model": "meta-llama/llama-4-scout-17b-16e-instruct",
+  "choices": [
+    {
+      "index": 0,
+      "message": {
+        "role": "assistant",
+        "content": "```java\nimport org.openqa.selenium.By;\nimport org.openqa.selenium.WebDriver;\nimport org.openqa.selenium.WebElement;\nimport org.openqa.selenium.chrome.ChromeDriver;\n\npublic class Main {\n    public static void main(String[] args) {\n        System.setProperty(\"webdriver.chrome.driver\", \"/path/to/chromedriver\");\n        WebDriver driver = new ChromeDriver();\n        driver.get(\"your_website_url\");\n\n        WebElement companyNameInput = driver.findElement(By.name(\"companyName\"));\n        WebElement lastNameInput = driver.findElement(By.name(\"lastName\"));\n        WebElement firstNameInput = driver.findElement(By.name(\"firstName\"));\n        WebElement submitButton = driver.findElement(By.className(\"smallSubmit\"));\n\n        companyNameInput.sendKeys(\"Company Name\");\n        lastNameInput.sendKeys(\"Last Name\");\n        firstNameInput.sendKeys(\"First Name\");\n        submitButton.click();\n\n        driver.quit();\n    }\n}\n```"
+      },
+      "logprobs": null,
+      "finish_reason": "stop"
+    }
+  ],
+  "usage": {
+    "queue_time": 0.056230321,
+    "prompt_tokens": 166,
+    "prompt_time": 0.00546659,
+    "completion_tokens": 187,
+    "completion_time": 0.447885634,
+    "total_tokens": 353,
+    "total_time": 0.453352224
+  },
+  "usage_breakdown": null,
+  "system_fingerprint": "fp_79da0e0073",
+  "x_groq": {
+    "id": "req_01kj5gv5x3em1sn7n0vb3x4mnd",
+    "seed": 1368404973
+  },
+  "service_tier": "on_demand"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "id": "stub",
+  "object": "chat.completion",
+  "created": 1771859754,
+  "model": "groq/compound-mini",
+  "choices": [
+    {
+      "index": 0,
+      "message": {
+        "role": "assistant",
+        "content": "28 °C / 24 °C (source: https://www.weather25.com/asia/india/tamil-nadu/chennai?page=month&amp;month=February)",
+        "reasoning": "&lt;tool&gt;search(Chennai temperature Feb 23 2026)&lt;/tool&gt;\n&lt;output&gt;Title: Weather Chennai in February 2026: Temperature &amp; Climate\nURL: https://en.climate-data.org/asia/india/tamil-nadu/chennai-1003222/t/february-2/\nContent: Climograph, Chennai\n\nIn February, Chennai sees its warmest day on 27.02 with a high of 31.1°C | 88°F,\nand its coldest on 08.02, where the temperature drops to 20.5°C | 68.9°F.\nDuring the first third of the month, average highs are 29.1°C | 84.4°F and lows 20.8°C | 69.4°F.\nThe second third brings highs of 30.1°C | 86.2°F and lows of 21.1°C | 70°F.\nAt month’s end, highs are around 30.9°C | 87.6°F, with lows at 21.3°C | 70.3°F.\nThe warmest 10-day block is from 21-28, averaging highs of 25.7°C | 78.3°F.\nThe coldest span occurs between 1-10, with average lows of 24.8°C | 76.6°F. [...] | 28. February | 26 °C | 79 °F | 31 °C | 88 °F | 21 °C | 71 °F | 28 °C | 82 °F | 5.1 mm | 0.2 inch. | [...] In February, the average temperature in Chennai is 25.3°C | 77.5°F.\nWater temperatures start at around 26.8°C | 80.2°F in the first third of the month, rise to 27.2°C | 81°F mid-month, and reach 27.6°C | 81.7°F toward the end.\n\nIn February, Chennai experiences daily rainfall amounts between 1.48/0.06 mm/in and 7.29/0.29 mm/in.\nThe wettest day is usually 07.02, with 7.29/0.29 mm/in, while 02.02 is the driest, seeing only 1.48/0.06 mm/in.\nIn the opening days of the month, rainfall averages 3.80/0.15 mm/in over 6 days.\nFrom days 11 to 20, it averages 3.80/0.15 mm/in, with 7 rainy days.\nToward month’s end, the average is 5.10/0.20 mm/in, and there are 7 rainy days.\nThe rainiest 10-day span falls between 21-28, averaging 5.10/0.20 mm/in.\nThe driest stretch is from 1-10, with 1.48/0.06 mm/in.\nScore: 1.0000\n\nTitle: Chennai weather in February 2026 - Weather25.com\nURL: https://www.weather25.com/asia/india/tamil-nadu/chennai?page=month&amp;month=February\nContent: ## The average weather in Chennai in February\n\nThe weather in Chennai in February is very hot. The average temperatures are between 24°C and 30°C, drinking water regularly is advisable.\n\nYou can expect a few rainy days in Chennai during February, but usually the weather is comfortable in February.\n\nOur weather forecast can give you a great sense of what weather to expect in Chennai in February 2026.\n\nIf you’re planning to visit Chennai in the near future, we highly recommend that you review the 14 day weather forecast for Chennai before you arrive.\n\nTemperatures\n\n30° / 24°\n\nRainy Days\n\n1\n\nSnowy Days\n\n0\n\nDry Days\n\n28\n\nRainfall\n\n15\n\nmm\n\nSun Hours\n\n11.9\n\nHrs\n\nHistoric average weather for February\n\nFebruary [...] United States England Australia Canada\n\n°F °C\n\nWeather in February 2026\n\n1. Home\n2. Asia\n3. India\n4. Tamil Nadu\n5. Chennai\n6. February\n\nLocation was added to My Locations\n\nLocation was removed from My Locations\n\n# Chennai weather in February 2026\n\nClick on a day for an hourly weather forecast\n\nFeb 13\n\n0 mm\n\n27° / 22°Feb 14\n\n0 mm\n\n27° / 22°Feb 15\n\n0 mm\n\n27° / 22°Feb 16\n\n0 mm\n\n28° / 23°Tuesday\n\nFeb 17\n\n0 mm\n\n28° / 23°Wednesday\n\nFeb 18\n\n0 mm\n\n27° / 23°Thursday\n\nFeb 19\n\n0 mm\n\n27° / 23°Friday\n\nFeb 20\n\n0.8 mm\n\n28° / 24°Saturday\n\nFeb 21\n\n2.3 mm\n\n25° / 25°Sunday\n\nFeb 22\n\n8.5 mm\n\n25° / 24°Monday\n\nFeb 23\n\n0.8 mm\n\n28° / 24°Tuesday\n\nFeb 24\n\n0 mm\n\n29° / 24°Wednesday\n\nFeb 25\n\n0 mm\n\n29° / 25°Thursday\n\nFeb 26\n\n0.3 mm\n\n29° / 26° Next  \nMonth &gt;&gt;\n\n## The average weather in Chennai in February [...] Temperatures in Chennai in February\n\nRain in Chennai in February\n\n## Recommended Hotels in Chennai\n\nWe know that finding the ideal hotel in Chennai can be a hard task...\n\nThat’s why we run our special tools and found the best hotels in Chennai. Click on hotel for more details.\n\nNovotel Chennai Chamiers Road\n\nBook NowNovotel Chennai OMR\n\nBook NowCitadines OMR Chennai\n\nBook Now\n\n## Weather in Chennai in February - FAQ\n\nWhat is the average temperature in Chennai in February?\n\nThe average temperature in Chennai in February is 24/30° C.\n\nWhat is the chance of rain in Chennai in February?\n\nOn average, there are 1 rainy days in Chennai during February.\n\nWeather wise, is February a good time to visit Chennai?\n\nThe weather in Chennai in February is good.\n\nCan it snow in Chennai in February?\nScore: 0.9999\n\nTitle: Chennai February 2026 Historical Weather Data (Tamil ...\nURL: https://weatherspark.com/h/m/110123/2026/2/Historical-Weather-in-February-2026-in-Chennai-Tamil-Nadu-India\nContent: |  |  --- | | Vis. | 3.73 mi | | Alt. | 29.77 inHg |  Raw: VOMM 210830Z 07013KT 6000 SCT020 SCT100 31/24 Q1008 NOSIG  This report shows the past weather for Chennai, providing a weather history for February 2026. It features all historical weather data series we have available, including the Chennai temperature history for February 2026. You can drill down from year to month and even day level reports by clicking on the graphs.  Chennai Temperature History February 2026 Winter 2026  Link  Download  Compare  Averages  History:JFebMAMJJASOND2025202420232022  The daily range of reported temperatures (gray bars) and 24-hour highs (red ticks) and lows (blue ticks), placed over the daily average high (faint red line) and low (faint blue line) temperature, with 25th to 75th and 10th to 90th [...] blue line) temperature, with 25th to 75th and 10th to 90th percentile bands.  Hourly Temperature in February 2026 in Chennai Winter 2026  Link  Download  Compare  Averages  History:JFebMAMJJASOND2025202420232022  frigid   15°F   freezing   32°F   very cold   45°F   cold   55°F   cool   65°F   comfortable   75°F   warm   85°F   hot   95°F   sweltering  The hourly reported temperature, color coded into bands. The shaded overlays indicate night and civil twilight.  © OpenStreetMap contributors  Compare Chennai to another city:  Cloud Cover in February 2026 in Chennai Winter 2026  Link  Download  Compare  Averages  History:JFebMAMJJASOND2025202420232022  0%   clear   20%   mostly clear   40%   partly cloudy   60%   mostly cloudy   80%   overcast   100%  no significant cloudno cloud [...] | ---   194019501960197019801990200020102020   ---   2017201820192020202120222023202420252026   ---   SpringSummerFallWinter  JanFebMarAprMayJunJulAugSepOctNovDec   ---   12345678910111213141516171819202122232425262728 February 2026 Weather History in Chennai Tamil Nadu, India The data for this report comes from the Chennai International Airport. See all nearby weather stations  Latest Report — 2:00 PM Sat, Feb 21, 2026    17 min ago    UTC 08:30  Call Sign VOMM  Temp.  88°F hot   |  |  |  --- | | Dew Pt. | 75°F  miserable | | Rel. Humidity | 66% |  Precipitation  No Report  Wind  15.0 mph moderate breeze   |  |  |  --- | | Wind Dir. | 70 deg, ENE |  Cloud Cover  Partly Cloudy   2,000 ft   |  |  | Partly Cloudy 10,000 ft |   |  |  |  --- | | Vis. | 3.73 mi | | Alt. | 29.77 inHg |  Raw:\nScore: 0.9998\n\nTitle: Weather in Chennai in February 2026 - Detailed Forecast\nURL: https://www.easeweather.com/asia/india/tamil-nadu/chennai/february\nContent: ### Temperatures\n\n Until now, February 2026 in Chennai is slightly cooler than the historical average by -1.2 °C.\n The forecast for the next days in Chennai predicts temperatures to be around 30 °C, close to the historical average.\n In general, the average temperature in Chennai at the beginning of February is 27.7 °C. As the month progressed, temperatures tended to moderately rise, reaching an average of 29.3 °C by the end of February.\n\n### Rain 🌧️\n\n Precipitation in Chennai during February is a rare event, with an average of fewer than 2 rainy days.\n\n29\n\nDry days\n\n0\n\nRainy days\n\n0\n\nSnow days\n\n28°/23°\n\nTemperatures\n\n18 km/h\n\nAvg max wind\n\n68 %\n\nAvg humidity\n\n## Chennai Weather February\n\nMove between months or click on a day\n\nJanuary\nMarch [...] | 16 Feb. | Sunny | 28° /22° | 0 mm | 8 |\n| 17 Feb. | Sunny | 28° /22° | 0 mm | 8 |\n| 18 Feb. | Sunny | 28° /22° | 0 mm | 8 |\n| 19 Feb. | Sunny | 28° /22° | 0 mm | 8 |\n| 20 Feb. | Sunny | 28° /23° | 0 mm | 8 |\n| 21 Feb. | Sunny | 29° /23° | 0 mm | 8 |\n| 22 Feb. | Patchy rain possible | 28° /25° | 0.7 mm | 2.4 |\n| 23 Feb. | Patchy rain possible | 29° /25° | 0.2 mm | 2.1 |\n| 24 Feb. | Sunny | 29° /24° | 0 mm | 2.3 |\n| 25 Feb. | Sunny | 29° /24° | 0 mm | 2.2 |\n| 26 Feb. | Sunny | 29° /24° | 0 mm | 2.9 |\n| 27 Feb. | Sunny | 30° /24° | 0 mm | 7 |\n| 28 Feb. | Sunny | 31° /24° | 0 mm | 7 |\n| Next | [...] Date | Weather | Temperatures | Rain | UV | More || 1 Feb. | Partly cloudy | 28° /23° | 0.1 mm | 7 |\n| 2 Feb. | Patchy rain possible | 28° /23° | 0 mm | 7 |\n| 3 Feb. | Partly cloudy | 27° /22° | 0 mm | 7 |\n| 4 Feb. | Sunny | 28° /22° | 0 mm | 7 |\n| 5 Feb. | Sunny | 27° /22° | 0 mm | 7 |\n| 6 Feb. | Partly cloudy | 28° /22° | 0 mm | 7 |\n| 7 Feb. | Sunny | 28° /21° | 0 mm | 7 |\n| 8 Feb. | Sunny | 28° /22° | 0 mm | 7 |\n| 9 Feb. | Sunny | 28° /22° | 0 mm | 7 |\n| 10 Feb. | Partly cloudy | 27° /23° | 0.1 mm | 7 |\n| 11 Feb. | Patchy rain possible | 27° /23° | 0 mm | 7 |\n| 12 Feb. | Cloudy | 27° /21° | 0 mm | 7 |\n| 13 Feb. | Sunny | 27° /22° | 0 mm | 7 |\n| 14 Feb. | Sunny | 28° /22° | 0 mm | 7 |\n| 15 Feb. | Sunny | 28° /22° | 0 mm | 7 |\n| 16 Feb. | Sunny | 28° /22° | 0 mm | 8 |\nScore: 0.9997\n\nTitle: Nights get warmer in city, Feb could set the stage for ...\nURL: https://timesofindia.indiatimes.com/city/chennai/nights-get-warmer-in-city-feb-could-set-the-stage-for-summer-2026/articleshow/128042877.cms\nContent: Comments\n\nShare\n\nAA\n\nText Size\n\n Small\n Medium\n Large\n\nChennai: Nights are turning warmer in the city, with minimum temperatures staying above 20C since the start of the month. Is winter already behind us?The IMD's monthly outlook suggests Feb may not deliver the chill many expect, with night temperatures likely to hover around 21oC–22oC, close to the seasonal normal. Day temperatures, however, are expected to rise progressively as the month advances. While private forecasters broadly agree that winter has largely run its course and Feb could set the stage for summer 2026, bloggers say there is still a narrow window for cooler nights in the days ahead.\n\nChennai: Income Tax Penalty, GCC, H5N1 Avian Flu &amp; More [...] Climatologically, the city records an average maximum temperature of 31.2oC and a minimum of 22.4oC in Feb.\"Minimum temperatures may remain around 21oC and maximum at 31oC at least for the next five days. But temperatures are likely to rise progressively through the month,\" said P Senthamarai Kannan, director, Regional Weather Forecasting Centre, IMD, Chennai.On Sunday, the IMD forecast dry weather to prevail, with shallow mist/haze likely during early morning hours. Partly cloudy skies may maintain temperatures at a maximum of around 31oC and a minimum of 21oC.Mahesh Palawat, chief meteorologist, Skymet Weather, said winter is nearing its end across most parts of India, with temperatures rising over north India.\"The easterlies and cloud cover are making nights warmer,\" he said.Blogger [...] conditions. Nungambakkam and Meenambakkam recorded 30.3oC and 31.2oC, near the normal temperature for the month.\nScore: 0.9984\n\nTitle: Chennai Weather Update: IMD Predicts Light Rainfall In The City ...\nURL: https://www.freepressjournal.in/india/chennai-weather-update-for-february-23\nContent: The minimum and maximum temperatures are expected to be around 24 degrees Celsius and 29 degrees Celsius, respectively. The humidity is likely to be around 69 per cent, and the wind is predicted to blow at a speed of 14 kmph.\n\nRainfall is expected in these regions\n\nThe weather department said that light to moderate rainfall is expected on Monday, February 23, 2026. Light to moderate rainfall is predicted in the Western Ghats regions in the upcoming days.\n\nLet us know! 👂  \nWhat type of content would you like to see from us this year?\n\narticle-image\n\nWhat you should do if you're in the affected area\n\nAvoid going to the sea; avoid being near the coast or beaches.\n\nStay indoors, especially when the wind picks up and the rain starts heavily. [...] # Chennai Weather Update: IMD Predicts Light Rainfall In The City &amp; Its Surrounding Areas; Here's To Know More\n\n## The minimum and maximum temperatures are expected to be around 24 degrees Celsius and 29 degrees Celsius, respectively. The humidity is likely to be around 69 per cent, and the wind is predicted to blow at a speed of 14 kmph.\n\narticle-image\n\nChennai: The India Meteorological Department (IMD) has stated that several districts of Tamil Nadu are likely to receive light to moderate rainfall in the next few days. The coastal regions are also likely to witness thunderstorms and gusty winds. The meteorological agency has recommended that residents adhere to the guidelines and limit outdoor activities to prevent disruptions.\n\nDeep Depression over Southwest Bay of Bengal [...] Secure anything loose outside (e.g., chairs, sheets, loose roofing), and close windows/doors firmly.\n\nCharge your phone, ensure you have a torch/flashlight, water bottles, and some food, and be ready for power cuts.\n\ngoogle-news-icon\nScore: 0.9969\n\nTitle: [PDF] Daily Weather Report for Tamilnadu, Puducherry &amp; Karaikal Area\nURL: https://mausam.imd.gov.in/chennai/mcdata/daily_weather_report.pdf\nContent: Erode, Perambalur, Kancheepuram, Ranipet and Vellore during early morning hours of 17th February. Shallow to Moderate Fog is likely to prevail at isolated pockets over Chennai and Tiruvallur districts of Tamilnadu during early morning hours of 18th February. Mist/Haze is likely to prevail at isolated pockets over Karur, Namakkal, Erode, Perambalur, Kancheepuram, Ranipet and Vellore during early morning hours of 18th February. TEMPERATURE FORECAST Maximum Temperature: Tendency: Gradual rise in maximum temperature during Day 1 (13.02.2026) to Day 3 (15.02.2026) over Tamilnadu, Puducherry &amp; Karaikal area thereafter no large change in maximum temperature Departure from normal: Maximum Temperature likely to be near normal over Tamilnadu, Puducherry &amp; Karaikal area during Day 1 (13.02.2026) to [...] Puducherry &amp; Karaikal area during Day 1 (13.02.2026) to Day 5 (17.02.2026). Minimum Temperature Tendency: Slight falling tendency in minimum temperature during Day 1 (13.02.2026) to Day 3 (15.02.2026) over Tamilnadu, Puducherry &amp; Karaikal area thereafter no large change in minimum temperature. Departure from normal: Minimum temperature likely to be near normal during Day 1 (13.02.2026) to Day 3 (15.02.2026) and above normal by 2°C at isolated pockets during Day 4 (16.02.2026) &amp; Day 5 (17.02.2026) over Tamilnadu, Puducherry &amp; Karaikal area. LOCAL FORECAST FOR CHENNAI CITY AND NEIGHBOURHOOD Day 1 (13.02.2026) Day 2 (14.02.2026) Maximum Temperature Around 31°C. Around 32°C. Minimum Temperature Around 22°C. Around 22°C. Sky Condition Partly cloudy sky. Partly cloudy sky. Weather Dry weather [...] from normal Year's total from Annual normal oC oC oC oC % % mm 1-1-2026 mm 1-1-2026 cm Adiramapattinam 30.0 -1.9 23.5 2.3 83 -2 0.0 80.9 36.1 8 124 Chennai 31.0 0.0 22.1 -0.1 76 -3 0.0 76.5 55.3 8 140 Chennai_AP 30.9 -0.5 21.9 0.3 80 0 0.0 58.1 30.3 6 138 Coimbatore_AP 31.0 -1.8 21.0 0.8 76 0 0.0 12.9 9.3 1 59 m Coonoor 21.2 0.2 11.4 0.4 79 9 0.0 450.4 389.8 45 159 Cuddalore 29.1 -1.7 21.4 0.1 84 0 0.0 42.2 -5.3 4 134 m Dharmapuri 30.2 -2.0 19.3 0.7 71 -4 0.0 2.0 -3.4 Tr 91 Erode 33.8 -0.2 19.0 -1.7 73 8 0.0 18.0 -- 2 -- Kanyakumari 33.0 0.9 23.7 -0.1 71 2 0.0 18.9 2.7 2 75 KarurParamathi 34.0 1.5 20.0 0.4 83 2 0.0 74.0 65.8 7 59 Karaikal 28.5 -1.7 23.8 1.0 95 13 0.0 181.1 117.7 18 150 Kodaikanal 19.8 0.6 7.9 -1.0 87 27 0.0 93.7 49.5 9 158 Madurai_City 32.2 -0.8 19.4 -2.7 68 -12 0.0 37.0\nScore: 0.9946\n\nTitle: Chennai, India (february 2026) - Historical Weather\nURL: https://predictwind.com/weather/india/tamil-nadu/chennai/february\nContent: # Chennai Weather History\n\nHistorical data for India\n\nThis data is based on historical weather records for Chennai, India in february 2026. The weather in this month is generally warm, with breezy conditions and a dry climate.\n\n### Temperature Trend (°C)\n\n## Avg Temp\n\n26°\nMonthly Average\n\n## Rainfall\n\n4.0mm\nTotal Monthly\n\n## Wind Avg\n\n9kt\nAverage Speed\n\n## Max Gust\n\n27kt\nHighest Gust\n\n### Daily Rainfall (mm)\n\n### Max Wind Gust (kt)\n\n## Daily View\n\nFebruary 2026\n\n| Su | Mo | Tu | We | Th | Fr | Sa |\n ---  ---  --- \n|  |  |  |  |  |  |  |\n|  |  |  |  |  |  |  |\n|  |  |  |  |  |  |  |\n|  |  |  |  |  |  |  |\n\n## Get the app for the world’s most accurate hi-res weather forecasts.\n\n4.8\n\n1M+ USERS / 30K RATINGS\n\nDownload for free now\n\n0.7\nScore: 0.9924\n\nTitle: Travel Advisory: Heavy Rainfall In South India, North &amp; West Get ...\nURL: https://www.travelandleisureasia.com/in/news/travel-advisory-south-india-braces-for-heavy-rainfall-north-west-to-get-warmer/\nContent: From February 23-26, weather conditions in the Andaman and Nicobar islands will also take a beating. With thunderstorms, lightning, and strong winds in tow, ferry services, island excursions, and water sports may witness temporary operational disruptions.\n A rainfall warning has been sounded for Himachal Pradesh (February 23) and Uttarakhand (February 23-24).\n Over the next seven days, IMD has also forecast a gradual rise in maximum temperatures by 3-4 degrees Celsius across northwest India.\n\n## Related Stories\n\n## Got travel plans in south India? Here’s what to keep in mind\n\n&gt; The Regional Meteorological Centre (RMC) in Chennai has issued a heavy rainfall alert for parts of southern Tamil Nadu on Sunday…#OmmcomNews\n&gt;\n&gt; — Ommcom News (@OmmcomNews) February 22, 2026 [...] The Indian Meteorological Department (IMD) has issued a travel advisory highlighting a dual weather pattern: heavy rainfall and chilly winds in south India, and warmer temperatures across northern and western states. The forecast suggests that thunderstorm showers will drench parts of south India until February 23 (although weather activity may continue to intensify over the next 36 hours), and then travel towards east and central India, triggering thunderstorm warnings.\n\nThose planning to travel to the south India’s coastal regions, especially beaches and backwaters, are advised to alter their plans based on recent forecasts.\n\n## Weather advisory: Key state-wise takeaways [...] News Travel Advisory: South India Braces For Heavy Rainfall, North &amp; West To Get Warmer\n\n Share\n\nAdvertisement\n\n Home\n News\n Travel Advisory: South India Braces For Heavy Rainfall, North &amp; West To Get Warmer\n\n# Travel Advisory: South India Braces For Heavy Rainfall, North &amp; West To Get Warmer\n\n## Planning to travel to south India? Heavy rainfall, lightning, and thunder will impact beaches, backwaters, and hills, slowing down tourism.\n\nByYashita Vashishth Published: Feb 23, 2026 10:49 AM IST3 min read\n\nShare:\n\n### Highlights\n\n IMD has issued a weather warning across 12 Indian states, because of a low pressure area over the southwest Bay of Bengal.\n Heavy rainfall, gusty winds, and thunder has been forecast for several regions across a week, starting February 23.\nScore: 0.9086\n\n&lt;/output&gt;",
+        "executed_tools": [
+          {
+            "index": 0,
+            "type": "search",
+            "arguments": "{\"query\": \"Chennai temperature Feb 23 2026\"}",
+            "output": "Title: Weather Chennai in February 2026: Temperature &amp; Climate\nURL: https://en.climate-data.org/asia/india/tamil-nadu/chennai-1003222/t/february-2/\nContent: Climograph, Chennai\n\nIn February, Chennai sees its warmest day on 27.02 with a high of 31.1°C | 88°F,\nand its coldest on 08.02, where the temperature drops to 20.5°C | 68.9°F.\nDuring the first third of the month, average highs are 29.1°C | 84.4°F and lows 20.8°C | 69.4°F.\nThe second third brings highs of 30.1°C | 86.2°F and lows of 21.1°C | 70°F.\nAt month’s end, highs are around 30.9°C | 87.6°F, with lows at 21.3°C | 70.3°F.\nThe warmest 10-day block is from 21-28, averaging highs of 25.7°C | 78.3°F.\nThe coldest span occurs between 1-10, with average lows of 24.8°C | 76.6°F. [...] | 28. February | 26 °C | 79 °F | 31 °C | 88 °F | 21 °C | 71 °F | 28 °C | 82 °F | 5.1 mm | 0.2 inch. | [...] In February, the average temperature in Chennai is 25.3°C | 77.5°F.\nWater temperatures start at around 26.8°C | 80.2°F in the first third of the month, rise to 27.2°C | 81°F mid-month, and reach 27.6°C | 81.7°F toward the end.\n\nIn February, Chennai experiences daily rainfall amounts between 1.48/0.06 mm/in and 7.29/0.29 mm/in.\nThe wettest day is usually 07.02, with 7.29/0.29 mm/in, while 02.02 is the driest, seeing only 1.48/0.06 mm/in.\nIn the opening days of the month, rainfall averages 3.80/0.15 mm/in over 6 days.\nFrom days 11 to 20, it averages 3.80/0.15 mm/in, with 7 rainy days.\nToward month’s end, the average is 5.10/0.20 mm/in, and there are 7 rainy days.\nThe rainiest 10-day span falls between 21-28, averaging 5.10/0.20 mm/in.\nThe driest stretch is from 1-10, with 1.48/0.06 mm/in.\nScore: 1.0000\n\nTitle: Chennai weather in February 2026 - Weather25.com\nURL: https://www.weather25.com/asia/india/tamil-nadu/chennai?page=month&amp;month=February\nContent: ## The average weather in Chennai in February\n\nThe weather in Chennai in February is very hot. The average temperatures are between 24°C and 30°C, drinking water regularly is advisable.\n\nYou can expect a few rainy days in Chennai during February, but usually the weather is comfortable in February.\n\nOur weather forecast can give you a great sense of what weather to expect in Chennai in February 2026.\n\nIf you’re planning to visit Chennai in the near future, we highly recommend that you review the 14 day weather forecast for Chennai before you arrive.\n\nTemperatures\n\n30° / 24°\n\nRainy Days\n\n1\n\nSnowy Days\n\n0\n\nDry Days\n\n28\n\nRainfall\n\n15\n\nmm\n\nSun Hours\n\n11.9\n\nHrs\n\nHistoric average weather for February\n\nFebruary [...] United States England Australia Canada\n\n°F °C\n\nWeather in February 2026\n\n1. Home\n2. Asia\n3. India\n4. Tamil Nadu\n5. Chennai\n6. February\n\nLocation was added to My Locations\n\nLocation was removed from My Locations\n\n# Chennai weather in February 2026\n\nClick on a day for an hourly weather forecast\n\nFeb 13\n\n0 mm\n\n27° / 22°Feb 14\n\n0 mm\n\n27° / 22°Feb 15\n\n0 mm\n\n27° / 22°Feb 16\n\n0 mm\n\n28° / 23°Tuesday\n\nFeb 17\n\n0 mm\n\n28° / 23°Wednesday\n\nFeb 18\n\n0 mm\n\n27° / 23°Thursday\n\nFeb 19\n\n0 mm\n\n27° / 23°Friday\n\nFeb 20\n\n0.8 mm\n\n28° / 24°Saturday\n\nFeb 21\n\n2.3 mm\n\n25° / 25°Sunday\n\nFeb 22\n\n8.5 mm\n\n25° / 24°Monday\n\nFeb 23\n\n0.8 mm\n\n28° / 24°Tuesday\n\nFeb 24\n\n0 mm\n\n29° / 24°Wednesday\n\nFeb 25\n\n0 mm\n\n29° / 25°Thursday\n\nFeb 26\n\n0.3 mm\n\n29° / 26° Next  \nMonth &gt;&gt;\n\n## The average weather in Chennai in February [...] Temperatures in Chennai in February\n\nRain in Chennai in February\n\n## Recommended Hotels in Chennai\n\nWe know that finding the ideal hotel in Chennai can be a hard task...\n\nThat’s why we run our special tools and found the best hotels in Chennai. Click on hotel for more details.\n\nNovotel Chennai Chamiers Road\n\nBook NowNovotel Chennai OMR\n\nBook NowCitadines OMR Chennai\n\nBook Now\n\n## Weather in Chennai in February - FAQ\n\nWhat is the average temperature in Chennai in February?\n\nThe average temperature in Chennai in February is 24/30° C.\n\nWhat is the chance of rain in Chennai in February?\n\nOn average, there are 1 rainy days in Chennai during February.\n\nWeather wise, is February a good time to visit Chennai?\n\nThe weather in Chennai in February is good.\n\nCan it snow in Chennai in February?\nScore: 0.9999\n\nTitle: Chennai February 2026 Historical Weather Data (Tamil ...\nURL: https://weatherspark.com/h/m/110123/2026/2/Historical-Weather-in-February-2026-in-Chennai-Tamil-Nadu-India\nContent: |  |  --- | | Vis. | 3.73 mi | | Alt. | 29.77 inHg |  Raw: VOMM 210830Z 07013KT 6000 SCT020 SCT100 31/24 Q1008 NOSIG  This report shows the past weather for Chennai, providing a weather history for February 2026. It features all historical weather data series we have available, including the Chennai temperature history for February 2026. You can drill down from year to month and even day level reports by clicking on the graphs.  Chennai Temperature History February 2026 Winter 2026  Link  Download  Compare  Averages  History:JFebMAMJJASOND2025202420232022  The daily range of reported temperatures (gray bars) and 24-hour highs (red ticks) and lows (blue ticks), placed over the daily average high (faint red line) and low (faint blue line) temperature, with 25th to 75th and 10th to 90th [...] blue line) temperature, with 25th to 75th and 10th to 90th percentile bands.  Hourly Temperature in February 2026 in Chennai Winter 2026  Link  Download  Compare  Averages  History:JFebMAMJJASOND2025202420232022  frigid   15°F   freezing   32°F   very cold   45°F   cold   55°F   cool   65°F   comfortable   75°F   warm   85°F   hot   95°F   sweltering  The hourly reported temperature, color coded into bands. The shaded overlays indicate night and civil twilight.  © OpenStreetMap contributors  Compare Chennai to another city:  Cloud Cover in February 2026 in Chennai Winter 2026  Link  Download  Compare  Averages  History:JFebMAMJJASOND2025202420232022  0%   clear   20%   mostly clear   40%   partly cloudy   60%   mostly cloudy   80%   overcast   100%  no significant cloudno cloud [...] | ---   194019501960197019801990200020102020   ---   2017201820192020202120222023202420252026   ---   SpringSummerFallWinter  JanFebMarAprMayJunJulAugSepOctNovDec   ---   12345678910111213141516171819202122232425262728 February 2026 Weather History in Chennai Tamil Nadu, India The data for this report comes from the Chennai International Airport. See all nearby weather stations  Latest Report — 2:00 PM Sat, Feb 21, 2026    17 min ago    UTC 08:30  Call Sign VOMM  Temp.  88°F hot   |  |  |  --- | | Dew Pt. | 75°F  miserable | | Rel. Humidity | 66% |  Precipitation  No Report  Wind  15.0 mph moderate breeze   |  |  |  --- | | Wind Dir. | 70 deg, ENE |  Cloud Cover  Partly Cloudy   2,000 ft   |  |  | Partly Cloudy 10,000 ft |   |  |  |  --- | | Vis. | 3.73 mi | | Alt. | 29.77 inHg |  Raw:\nScore: 0.9998\n\nTitle: Weather in Chennai in February 2026 - Detailed Forecast\nURL: https://www.easeweather.com/asia/india/tamil-nadu/chennai/february\nContent: ### Temperatures\n\n Until now, February 2026 in Chennai is slightly cooler than the historical average by -1.2 °C.\n The forecast for the next days in Chennai predicts temperatures to be around 30 °C, close to the historical average.\n In general, the average temperature in Chennai at the beginning of February is 27.7 °C. As the month progressed, temperatures tended to moderately rise, reaching an average of 29.3 °C by the end of February.\n\n### Rain 🌧️\n\n Precipitation in Chennai during February is a rare event, with an average of fewer than 2 rainy days.\n\n29\n\nDry days\n\n0\n\nRainy days\n\n0\n\nSnow days\n\n28°/23°\n\nTemperatures\n\n18 km/h\n\nAvg max wind\n\n68 %\n\nAvg humidity\n\n## Chennai Weather February\n\nMove between months or click on a day\n\nJanuary\nMarch [...] | 16 Feb. | Sunny | 28° /22° | 0 mm | 8 |\n| 17 Feb. | Sunny | 28° /22° | 0 mm | 8 |\n| 18 Feb. | Sunny | 28° /22° | 0 mm | 8 |\n| 19 Feb. | Sunny | 28° /22° | 0 mm | 8 |\n| 20 Feb. | Sunny | 28° /23° | 0 mm | 8 |\n| 21 Feb. | Sunny | 29° /23° | 0 mm | 8 |\n| 22 Feb. | Patchy rain possible | 28° /25° | 0.7 mm | 2.4 |\n| 23 Feb. | Patchy rain possible | 29° /25° | 0.2 mm | 2.1 |\n| 24 Feb. | Sunny | 29° /24° | 0 mm | 2.3 |\n| 25 Feb. | Sunny | 29° /24° | 0 mm | 2.2 |\n| 26 Feb. | Sunny | 29° /24° | 0 mm | 2.9 |\n| 27 Feb. | Sunny | 30° /24° | 0 mm | 7 |\n| 28 Feb. | Sunny | 31° /24° | 0 mm | 7 |\n| Next | [...] Date | Weather | Temperatures | Rain | UV | More || 1 Feb. | Partly cloudy | 28° /23° | 0.1 mm | 7 |\n| 2 Feb. | Patchy rain possible | 28° /23° | 0 mm | 7 |\n| 3 Feb. | Partly cloudy | 27° /22° | 0 mm | 7 |\n| 4 Feb. | Sunny | 28° /22° | 0 mm | 7 |\n| 5 Feb. | Sunny | 27° /22° | 0 mm | 7 |\n| 6 Feb. | Partly cloudy | 28° /22° | 0 mm | 7 |\n| 7 Feb. | Sunny | 28° /21° | 0 mm | 7 |\n| 8 Feb. | Sunny | 28° /22° | 0 mm | 7 |\n| 9 Feb. | Sunny | 28° /22° | 0 mm | 7 |\n| 10 Feb. | Partly cloudy | 27° /23° | 0.1 mm | 7 |\n| 11 Feb. | Patchy rain possible | 27° /23° | 0 mm | 7 |\n| 12 Feb. | Cloudy | 27° /21° | 0 mm | 7 |\n| 13 Feb. | Sunny | 27° /22° | 0 mm | 7 |\n| 14 Feb. | Sunny | 28° /22° | 0 mm | 7 |\n| 15 Feb. | Sunny | 28° /22° | 0 mm | 7 |\n| 16 Feb. | Sunny | 28° /22° | 0 mm | 8 |\nScore: 0.9997\n\nTitle: Nights get warmer in city, Feb could set the stage for ...\nURL: https://timesofindia.indiatimes.com/city/chennai/nights-get-warmer-in-city-feb-could-set-the-stage-for-summer-2026/articleshow/128042877.cms\nContent: Comments\n\nShare\n\nAA\n\nText Size\n\n Small\n Medium\n Large\n\nChennai: Nights are turning warmer in the city, with minimum temperatures staying above 20C since the start of the month. Is winter already behind us?The IMD's monthly outlook suggests Feb may not deliver the chill many expect, with night temperatures likely to hover around 21oC–22oC, close to the seasonal normal. Day temperatures, however, are expected to rise progressively as the month advances. While private forecasters broadly agree that winter has largely run its course and Feb could set the stage for summer 2026, bloggers say there is still a narrow window for cooler nights in the days ahead.\n\nChennai: Income Tax Penalty, GCC, H5N1 Avian Flu &amp; More [...] Climatologically, the city records an average maximum temperature of 31.2oC and a minimum of 22.4oC in Feb.\"Minimum temperatures may remain around 21oC and maximum at 31oC at least for the next five days. But temperatures are likely to rise progressively through the month,\" said P Senthamarai Kannan, director, Regional Weather Forecasting Centre, IMD, Chennai.On Sunday, the IMD forecast dry weather to prevail, with shallow mist/haze likely during early morning hours. Partly cloudy skies may maintain temperatures at a maximum of around 31oC and a minimum of 21oC.Mahesh Palawat, chief meteorologist, Skymet Weather, said winter is nearing its end across most parts of India, with temperatures rising over north India.\"The easterlies and cloud cover are making nights warmer,\" he said.Blogger [...] conditions. Nungambakkam and Meenambakkam recorded 30.3oC and 31.2oC, near the normal temperature for the month.\nScore: 0.9984\n\nTitle: Chennai Weather Update: IMD Predicts Light Rainfall In The City ...\nURL: https://www.freepressjournal.in/india/chennai-weather-update-for-february-23\nContent: The minimum and maximum temperatures are expected to be around 24 degrees Celsius and 29 degrees Celsius, respectively. The humidity is likely to be around 69 per cent, and the wind is predicted to blow at a speed of 14 kmph.\n\nRainfall is expected in these regions\n\nThe weather department said that light to moderate rainfall is expected on Monday, February 23, 2026. Light to moderate rainfall is predicted in the Western Ghats regions in the upcoming days.\n\nLet us know! 👂  \nWhat type of content would you like to see from us this year?\n\narticle-image\n\nWhat you should do if you're in the affected area\n\nAvoid going to the sea; avoid being near the coast or beaches.\n\nStay indoors, especially when the wind picks up and the rain starts heavily. [...] # Chennai Weather Update: IMD Predicts Light Rainfall In The City &amp; Its Surrounding Areas; Here's To Know More\n\n## The minimum and maximum temperatures are expected to be around 24 degrees Celsius and 29 degrees Celsius, respectively. The humidity is likely to be around 69 per cent, and the wind is predicted to blow at a speed of 14 kmph.\n\narticle-image\n\nChennai: The India Meteorological Department (IMD) has stated that several districts of Tamil Nadu are likely to receive light to moderate rainfall in the next few days. The coastal regions are also likely to witness thunderstorms and gusty winds. The meteorological agency has recommended that residents adhere to the guidelines and limit outdoor activities to prevent disruptions.\n\nDeep Depression ov🌧</t>
   </si>
 </sst>
 </file>
@@ -2924,7 +3155,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="255">
+    <row r="16" spans="1:2" ht="210">
       <c r="B16" s="7" t="s">
         <v>20</v>
       </c>
@@ -3233,7 +3464,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="165" spans="2:4" ht="30">
+    <row r="165" spans="2:4">
       <c r="B165" s="2" t="s">
         <v>70</v>
       </c>
@@ -3506,7 +3737,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="240" spans="2:3" ht="30">
+    <row r="240" spans="2:3">
       <c r="B240" s="2" t="s">
         <v>108</v>
       </c>
@@ -3530,7 +3761,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="243" spans="2:3" ht="30">
+    <row r="243" spans="2:3">
       <c r="B243" s="3" t="s">
         <v>112</v>
       </c>
@@ -3809,7 +4040,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="369" spans="2:5" ht="60">
+    <row r="369" spans="2:5">
       <c r="B369" s="2" t="s">
         <v>108</v>
       </c>
@@ -3823,7 +4054,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="370" spans="2:5" ht="45">
+    <row r="370" spans="2:5">
       <c r="B370" s="3" t="s">
         <v>158</v>
       </c>
@@ -3837,7 +4068,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="371" spans="2:5" ht="75">
+    <row r="371" spans="2:5">
       <c r="B371" s="3" t="s">
         <v>162</v>
       </c>
@@ -3851,7 +4082,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="372" spans="2:5" ht="60">
+    <row r="372" spans="2:5" ht="30">
       <c r="B372" s="3" t="s">
         <v>166</v>
       </c>
@@ -3865,7 +4096,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="373" spans="2:5" ht="45">
+    <row r="373" spans="2:5">
       <c r="B373" s="3" t="s">
         <v>170</v>
       </c>
@@ -3879,7 +4110,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="374" spans="2:5" ht="75">
+    <row r="374" spans="2:5" ht="30">
       <c r="B374" s="3" t="s">
         <v>174</v>
       </c>
@@ -6731,11 +6962,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0749D211-9F69-477D-B783-91857F6EF137}">
-  <dimension ref="B1:B19"/>
+  <dimension ref="B1:B50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="58.7109375" customWidth="1"/>
+    <col min="2" max="2" width="71.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
@@ -6818,6 +7049,111 @@
         <v>564</v>
       </c>
     </row>
+    <row r="21" spans="2:2">
+      <c r="B21" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" ht="409.5">
+      <c r="B23" s="7" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2">
+      <c r="B25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" ht="409.5">
+      <c r="B27" s="7" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2">
+      <c r="B29" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" ht="409.5">
+      <c r="B31" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" ht="409.5">
+      <c r="B36" s="7" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" ht="409.5">
+      <c r="B41" s="7" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2">
+      <c r="B43" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2">
+      <c r="B44" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" ht="409.5">
+      <c r="B45" s="7" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2">
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2">
+      <c r="B48" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" ht="409.5">
+      <c r="B50" s="7" t="s">
+        <v>572</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
